--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/CONNECTICUT_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/CONNECTICUT_2011.xlsx
@@ -4837,7 +4837,7 @@
         <v>16</v>
       </c>
       <c r="D249">
-        <v>0.009714632665452</v>
+        <v>0.009714632665452002</v>
       </c>
     </row>
     <row r="250">
@@ -5053,7 +5053,7 @@
         <v>161</v>
       </c>
       <c r="D261">
-        <v>0.097753491196114</v>
+        <v>0.09775349119611401</v>
       </c>
     </row>
     <row r="262">
